--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/71.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/71.xlsx
@@ -426,13 +426,13 @@
         <v>1.457587930218217</v>
       </c>
       <c r="E2">
-        <v>-13.17624930228161</v>
+        <v>-8.082082850047081</v>
       </c>
       <c r="F2">
-        <v>-3.986645333347023</v>
+        <v>-4.543521468834123</v>
       </c>
       <c r="G2">
-        <v>-5.113387026988128</v>
+        <v>-2.314694865180277</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>1.623934615351854</v>
       </c>
       <c r="E3">
-        <v>-12.68588802283503</v>
+        <v>-8.737235298632783</v>
       </c>
       <c r="F3">
-        <v>-4.45125476220062</v>
+        <v>-5.046570607667267</v>
       </c>
       <c r="G3">
-        <v>-3.510020300862767</v>
+        <v>-2.132591686701586</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>1.651736239763865</v>
       </c>
       <c r="E4">
-        <v>-11.5829645928449</v>
+        <v>-10.71924874536193</v>
       </c>
       <c r="F4">
-        <v>-4.649309064720689</v>
+        <v>-4.887475470667008</v>
       </c>
       <c r="G4">
-        <v>-4.159420224391742</v>
+        <v>-0.988672402152899</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>1.536942890263834</v>
       </c>
       <c r="E5">
-        <v>-12.63457135538011</v>
+        <v>-9.218580386330087</v>
       </c>
       <c r="F5">
-        <v>-4.949535362522376</v>
+        <v>-4.561890081894347</v>
       </c>
       <c r="G5">
-        <v>-3.252827328462328</v>
+        <v>-0.742480372579458</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>1.306014652300521</v>
       </c>
       <c r="E6">
-        <v>-14.17000028089483</v>
+        <v>-10.9968306166101</v>
       </c>
       <c r="F6">
-        <v>-4.422714006045529</v>
+        <v>-4.881781256048045</v>
       </c>
       <c r="G6">
-        <v>-3.619582805484947</v>
+        <v>0.02081887022814258</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.987406830023096</v>
       </c>
       <c r="E7">
-        <v>-14.83001631056477</v>
+        <v>-11.94420096443676</v>
       </c>
       <c r="F7">
-        <v>-4.244240643463953</v>
+        <v>-4.730587227859915</v>
       </c>
       <c r="G7">
-        <v>-4.551617243883661</v>
+        <v>-2.488700449269909</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.6179790902944678</v>
       </c>
       <c r="E8">
-        <v>-15.72630094311091</v>
+        <v>-12.53702349678089</v>
       </c>
       <c r="F8">
-        <v>-4.5503147753584</v>
+        <v>-4.642310668280362</v>
       </c>
       <c r="G8">
-        <v>-2.528903714298819</v>
+        <v>-1.372420909428597</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.2358809421435074</v>
       </c>
       <c r="E9">
-        <v>-16.87887909059515</v>
+        <v>-13.60387763129993</v>
       </c>
       <c r="F9">
-        <v>-4.647304093031742</v>
+        <v>-4.488235879032047</v>
       </c>
       <c r="G9">
-        <v>-2.774880558412207</v>
+        <v>-1.653678237353999</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.118731588661553</v>
       </c>
       <c r="E10">
-        <v>-16.97270907203408</v>
+        <v>-15.02998013732147</v>
       </c>
       <c r="F10">
-        <v>-3.830387405494274</v>
+        <v>-4.201912143609045</v>
       </c>
       <c r="G10">
-        <v>-3.38232262777646</v>
+        <v>0.05053101644310148</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.407749857885213</v>
       </c>
       <c r="E11">
-        <v>-19.2785944513178</v>
+        <v>-15.99413300982056</v>
       </c>
       <c r="F11">
-        <v>-3.931464268135366</v>
+        <v>-4.155500058051176</v>
       </c>
       <c r="G11">
-        <v>-2.674309495474688</v>
+        <v>-0.3277716434204956</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.600895947804221</v>
       </c>
       <c r="E12">
-        <v>-18.01020058108739</v>
+        <v>-17.30067474509159</v>
       </c>
       <c r="F12">
-        <v>-3.990319531070842</v>
+        <v>-4.075594176087679</v>
       </c>
       <c r="G12">
-        <v>-2.716714273287212</v>
+        <v>-1.014766122093435</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.6788442096243654</v>
       </c>
       <c r="E13">
-        <v>-18.7669629294572</v>
+        <v>-15.6481892949526</v>
       </c>
       <c r="F13">
-        <v>-3.983377356190513</v>
+        <v>-4.191671109306856</v>
       </c>
       <c r="G13">
-        <v>-3.281165598278489</v>
+        <v>-0.9225839815524283</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.6288112283431487</v>
       </c>
       <c r="E14">
-        <v>-19.44423244509636</v>
+        <v>-16.91015726056613</v>
       </c>
       <c r="F14">
-        <v>-3.453996730954316</v>
+        <v>-4.54670313401824</v>
       </c>
       <c r="G14">
-        <v>-1.679622982745267</v>
+        <v>-0.8617162912673882</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.4520481366144302</v>
       </c>
       <c r="E15">
-        <v>-19.98631795465855</v>
+        <v>-18.14565629560482</v>
       </c>
       <c r="F15">
-        <v>-3.62710528974734</v>
+        <v>-3.625501787507957</v>
       </c>
       <c r="G15">
-        <v>-2.063553570025625</v>
+        <v>0.7682771526303305</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.1634669741048333</v>
       </c>
       <c r="E16">
-        <v>-21.48339523380231</v>
+        <v>-17.05639980016984</v>
       </c>
       <c r="F16">
-        <v>-3.294890508012649</v>
+        <v>-3.227310609189017</v>
       </c>
       <c r="G16">
-        <v>-2.210253774507349</v>
+        <v>0.6138368926777903</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.2186157382400814</v>
       </c>
       <c r="E17">
-        <v>-22.0819825135582</v>
+        <v>-17.37217029272469</v>
       </c>
       <c r="F17">
-        <v>-2.829554158143865</v>
+        <v>-3.553246788821948</v>
       </c>
       <c r="G17">
-        <v>-2.092080540937525</v>
+        <v>2.707492102623674</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.667082647708689</v>
       </c>
       <c r="E18">
-        <v>-22.30641821385235</v>
+        <v>-18.90857284015106</v>
       </c>
       <c r="F18">
-        <v>-3.352459801744789</v>
+        <v>-2.854765964464703</v>
       </c>
       <c r="G18">
-        <v>-1.375307705138842</v>
+        <v>1.329427863718954</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.148253205423443</v>
       </c>
       <c r="E19">
-        <v>-23.06039102223343</v>
+        <v>-21.96954050394774</v>
       </c>
       <c r="F19">
-        <v>-2.314025416697059</v>
+        <v>-3.161544845491521</v>
       </c>
       <c r="G19">
-        <v>-1.464099847047634</v>
+        <v>3.288698098589203</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.632230818033711</v>
       </c>
       <c r="E20">
-        <v>-24.72718645023666</v>
+        <v>-22.09883296534074</v>
       </c>
       <c r="F20">
-        <v>-2.749124861375315</v>
+        <v>-2.018294468136347</v>
       </c>
       <c r="G20">
-        <v>-0.5339921461527763</v>
+        <v>1.095345809728167</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.089990089880757</v>
       </c>
       <c r="E21">
-        <v>-24.90831635359546</v>
+        <v>-24.63429386291732</v>
       </c>
       <c r="F21">
-        <v>-1.701140729657485</v>
+        <v>-2.911601210505037</v>
       </c>
       <c r="G21">
-        <v>0.4266586478873974</v>
+        <v>2.121932739274005</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.495082131143572</v>
       </c>
       <c r="E22">
-        <v>-26.47415398207168</v>
+        <v>-22.81564964448889</v>
       </c>
       <c r="F22">
-        <v>-2.176746620534936</v>
+        <v>-2.197140793461008</v>
       </c>
       <c r="G22">
-        <v>0.072877198833182</v>
+        <v>2.029174563809165</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.827575630501418</v>
       </c>
       <c r="E23">
-        <v>-25.91200280418151</v>
+        <v>-25.92991744735586</v>
       </c>
       <c r="F23">
-        <v>-1.395601890362457</v>
+        <v>-2.15933377399468</v>
       </c>
       <c r="G23">
-        <v>0.2391063114510668</v>
+        <v>2.307223973107013</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.073426126044266</v>
       </c>
       <c r="E24">
-        <v>-27.54479392086114</v>
+        <v>-22.93819920808446</v>
       </c>
       <c r="F24">
-        <v>-1.108983585639183</v>
+        <v>-1.64473308421432</v>
       </c>
       <c r="G24">
-        <v>-1.289620854945886</v>
+        <v>1.682603482939482</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.223688932422783</v>
       </c>
       <c r="E25">
-        <v>-27.81522986012521</v>
+        <v>-24.49404702289977</v>
       </c>
       <c r="F25">
-        <v>-1.272178937254514</v>
+        <v>-1.223434052883203</v>
       </c>
       <c r="G25">
-        <v>-1.001014115923302</v>
+        <v>-0.1017011096347448</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.275521483706779</v>
       </c>
       <c r="E26">
-        <v>-28.03613335069338</v>
+        <v>-25.77364886629917</v>
       </c>
       <c r="F26">
-        <v>-1.478566700301625</v>
+        <v>-1.979245823232314</v>
       </c>
       <c r="G26">
-        <v>-1.604596089188764</v>
+        <v>1.196857067598839</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.233066081787676</v>
       </c>
       <c r="E27">
-        <v>-28.65860380236572</v>
+        <v>-25.65242614558784</v>
       </c>
       <c r="F27">
-        <v>-1.502315162356597</v>
+        <v>-1.355892840091685</v>
       </c>
       <c r="G27">
-        <v>-0.4142166085419449</v>
+        <v>0.3703992369930229</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.105981920838601</v>
       </c>
       <c r="E28">
-        <v>-28.50528778636203</v>
+        <v>-24.64925141256465</v>
       </c>
       <c r="F28">
-        <v>-1.663219683365245</v>
+        <v>-1.995563537132044</v>
       </c>
       <c r="G28">
-        <v>-1.867185250818215</v>
+        <v>0.3820655994734145</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.907199777337046</v>
       </c>
       <c r="E29">
-        <v>-29.61778893887839</v>
+        <v>-24.78915408855762</v>
       </c>
       <c r="F29">
-        <v>-1.439352558129429</v>
+        <v>-1.577577618576026</v>
       </c>
       <c r="G29">
-        <v>-0.8174079497697827</v>
+        <v>0.7090415612961511</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.656141022877536</v>
       </c>
       <c r="E30">
-        <v>-29.80388884246061</v>
+        <v>-25.28654808813811</v>
       </c>
       <c r="F30">
-        <v>-0.9712534332911605</v>
+        <v>-2.447304563569738</v>
       </c>
       <c r="G30">
-        <v>-1.251877325252655</v>
+        <v>0.415581562512996</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.375142317764297</v>
       </c>
       <c r="E31">
-        <v>-28.77788833620177</v>
+        <v>-25.10610651282848</v>
       </c>
       <c r="F31">
-        <v>-1.541140504726553</v>
+        <v>-2.475919753902856</v>
       </c>
       <c r="G31">
-        <v>-1.728390629084271</v>
+        <v>1.458012763009786</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.085204927253238</v>
       </c>
       <c r="E32">
-        <v>-29.60417181753733</v>
+        <v>-23.51955111576716</v>
       </c>
       <c r="F32">
-        <v>-1.427450216321944</v>
+        <v>-2.090173336667439</v>
       </c>
       <c r="G32">
-        <v>-1.725546870466037</v>
+        <v>1.342365475686426</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.810197917638216</v>
       </c>
       <c r="E33">
-        <v>-29.46492577027547</v>
+        <v>-26.5418184406943</v>
       </c>
       <c r="F33">
-        <v>-1.451783857712671</v>
+        <v>-2.167315651808495</v>
       </c>
       <c r="G33">
-        <v>-1.023204702673037</v>
+        <v>1.329096809165027</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.57256488893098</v>
       </c>
       <c r="E34">
-        <v>-30.50828165316872</v>
+        <v>-24.478831350234</v>
       </c>
       <c r="F34">
-        <v>-1.296188710785534</v>
+        <v>-1.549798624966261</v>
       </c>
       <c r="G34">
-        <v>-0.4384829073448027</v>
+        <v>0.9484271092408506</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.387881791457772</v>
       </c>
       <c r="E35">
-        <v>-27.07574816856867</v>
+        <v>-24.15010942201721</v>
       </c>
       <c r="F35">
-        <v>-1.632616942108251</v>
+        <v>-1.578575353302753</v>
       </c>
       <c r="G35">
-        <v>-1.871065210190241</v>
+        <v>0.8225436151100638</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.268525026355692</v>
       </c>
       <c r="E36">
-        <v>-28.10682735842712</v>
+        <v>-23.68337771994265</v>
       </c>
       <c r="F36">
-        <v>-1.364235802854221</v>
+        <v>-1.328591333815425</v>
       </c>
       <c r="G36">
-        <v>-0.4656194491302086</v>
+        <v>0.2686661725712193</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.226553675519857</v>
       </c>
       <c r="E37">
-        <v>-27.65358598042141</v>
+        <v>-25.46837084802008</v>
       </c>
       <c r="F37">
-        <v>-1.16017450379689</v>
+        <v>-1.929545964193993</v>
       </c>
       <c r="G37">
-        <v>-0.7167177071928496</v>
+        <v>0.02385795103319353</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.26423976847049</v>
       </c>
       <c r="E38">
-        <v>-27.5325489271444</v>
+        <v>-23.0816839070175</v>
       </c>
       <c r="F38">
-        <v>-1.517118853401167</v>
+        <v>-2.084445864224252</v>
       </c>
       <c r="G38">
-        <v>-0.7436821006102133</v>
+        <v>1.273178384461197</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.376339671326067</v>
       </c>
       <c r="E39">
-        <v>-29.09493132995278</v>
+        <v>-24.18413637571084</v>
       </c>
       <c r="F39">
-        <v>-1.634554606295791</v>
+        <v>-1.067029632233277</v>
       </c>
       <c r="G39">
-        <v>-0.1331744660765959</v>
+        <v>1.580936629428464</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.560388053970287</v>
       </c>
       <c r="E40">
-        <v>-28.40926149502938</v>
+        <v>-23.1826417065445</v>
       </c>
       <c r="F40">
-        <v>-1.275275874172156</v>
+        <v>-1.737284857912602</v>
       </c>
       <c r="G40">
-        <v>-0.7260468245225158</v>
+        <v>1.933317717719568</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.805161643167374</v>
       </c>
       <c r="E41">
-        <v>-28.46342204416112</v>
+        <v>-21.84359005637241</v>
       </c>
       <c r="F41">
-        <v>-1.701974550821964</v>
+        <v>-1.493527970084781</v>
       </c>
       <c r="G41">
-        <v>-0.7172672577523685</v>
+        <v>0.1437957053754494</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.092339174480438</v>
       </c>
       <c r="E42">
-        <v>-28.24210646245825</v>
+        <v>-21.3867440130566</v>
       </c>
       <c r="F42">
-        <v>-1.129513957273982</v>
+        <v>-1.648065201460405</v>
       </c>
       <c r="G42">
-        <v>-0.5539812201188958</v>
+        <v>1.613681235357396</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.409562307798961</v>
       </c>
       <c r="E43">
-        <v>-26.77446879283836</v>
+        <v>-22.2492960427196</v>
       </c>
       <c r="F43">
-        <v>-1.125572905103411</v>
+        <v>-1.253981364433157</v>
       </c>
       <c r="G43">
-        <v>-0.3350912596078242</v>
+        <v>2.479094255323816</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.741040035130034</v>
       </c>
       <c r="E44">
-        <v>-26.8596267465526</v>
+        <v>-21.13114335464166</v>
       </c>
       <c r="F44">
-        <v>-1.513842165862123</v>
+        <v>-1.437910593893421</v>
       </c>
       <c r="G44">
-        <v>-0.7987695783836859</v>
+        <v>1.995142155665457</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.066825495522252</v>
       </c>
       <c r="E45">
-        <v>-26.26665477456622</v>
+        <v>-21.42649042942192</v>
       </c>
       <c r="F45">
-        <v>-0.7187703258692689</v>
+        <v>-1.431008011660978</v>
       </c>
       <c r="G45">
-        <v>0.1412432747646713</v>
+        <v>1.968479021892167</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.374063812748669</v>
       </c>
       <c r="E46">
-        <v>-26.37671480684864</v>
+        <v>-19.91706400165925</v>
       </c>
       <c r="F46">
-        <v>-0.6521667817425052</v>
+        <v>-1.010468367316314</v>
       </c>
       <c r="G46">
-        <v>-1.65834941710991</v>
+        <v>2.026056029911172</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.651882883935133</v>
       </c>
       <c r="E47">
-        <v>-26.27593361780794</v>
+        <v>-19.06206999511505</v>
       </c>
       <c r="F47">
-        <v>-1.290655242316988</v>
+        <v>-1.755487181851705</v>
       </c>
       <c r="G47">
-        <v>-0.8065261865821983</v>
+        <v>2.365343910594458</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.888329774284823</v>
       </c>
       <c r="E48">
-        <v>-25.36912028319397</v>
+        <v>-19.62163088587284</v>
       </c>
       <c r="F48">
-        <v>-1.452435552696874</v>
+        <v>-0.8136952828818362</v>
       </c>
       <c r="G48">
-        <v>-1.435966831054908</v>
+        <v>-0.8860454904354922</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.075319997301583</v>
       </c>
       <c r="E49">
-        <v>-25.98595731320077</v>
+        <v>-19.41654535501347</v>
       </c>
       <c r="F49">
-        <v>-0.8282257846559932</v>
+        <v>-2.317187285557234</v>
       </c>
       <c r="G49">
-        <v>-0.6694629801652926</v>
+        <v>1.636318745754932</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.210554469478638</v>
       </c>
       <c r="E50">
-        <v>-25.3518984965428</v>
+        <v>-19.32188213435712</v>
       </c>
       <c r="F50">
-        <v>-1.458148771786822</v>
+        <v>-1.364429014975904</v>
       </c>
       <c r="G50">
-        <v>-2.019503451080083</v>
+        <v>0.4869701665218399</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.291734159463328</v>
       </c>
       <c r="E51">
-        <v>-24.1691788260635</v>
+        <v>-19.71469102673046</v>
       </c>
       <c r="F51">
-        <v>-1.265052260635037</v>
+        <v>-1.324865665649354</v>
       </c>
       <c r="G51">
-        <v>-0.4747830391829112</v>
+        <v>1.272224947345887</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.317581657623717</v>
       </c>
       <c r="E52">
-        <v>-24.53438214088609</v>
+        <v>-18.60199062135776</v>
       </c>
       <c r="F52">
-        <v>-1.029520349479051</v>
+        <v>-1.611836344938812</v>
       </c>
       <c r="G52">
-        <v>-1.249940656112181</v>
+        <v>-0.5667135782629328</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.29472920402213</v>
       </c>
       <c r="E53">
-        <v>-24.03012297470997</v>
+        <v>-18.31719941948938</v>
       </c>
       <c r="F53">
-        <v>-1.331242457517871</v>
+        <v>-1.753651666695711</v>
       </c>
       <c r="G53">
-        <v>-0.7285992551332938</v>
+        <v>0.9714122269200105</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.228799655745858</v>
       </c>
       <c r="E54">
-        <v>-23.64579591415299</v>
+        <v>-16.53332935296585</v>
       </c>
       <c r="F54">
-        <v>-1.313221467906085</v>
+        <v>-1.270470910424712</v>
       </c>
       <c r="G54">
-        <v>-1.201120041044549</v>
+        <v>1.116563096089356</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.123320164935606</v>
       </c>
       <c r="E55">
-        <v>-22.98649085490226</v>
+        <v>-17.39781504103012</v>
       </c>
       <c r="F55">
-        <v>-1.320695767974001</v>
+        <v>-1.632445110016426</v>
       </c>
       <c r="G55">
-        <v>-2.200600223714834</v>
+        <v>0.5267033340841727</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.98866663343995</v>
       </c>
       <c r="E56">
-        <v>-23.69766958391086</v>
+        <v>-16.0878543078833</v>
       </c>
       <c r="F56">
-        <v>-1.066504633722308</v>
+        <v>-1.434360717083964</v>
       </c>
       <c r="G56">
-        <v>-1.56328048085866</v>
+        <v>0.3936657510430208</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.833723394451015</v>
       </c>
       <c r="E57">
-        <v>-21.66568442650707</v>
+        <v>-15.93220612776567</v>
       </c>
       <c r="F57">
-        <v>-1.357633332892753</v>
+        <v>-1.797482311611413</v>
       </c>
       <c r="G57">
-        <v>-2.414689893193963</v>
+        <v>0.5995883046767672</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>3.663147039143497</v>
       </c>
       <c r="E58">
-        <v>-23.70966098308317</v>
+        <v>-14.96346591109681</v>
       </c>
       <c r="F58">
-        <v>-1.05059947521355</v>
+        <v>-1.54634693792356</v>
       </c>
       <c r="G58">
-        <v>-2.158635748459033</v>
+        <v>-0.2692875459237308</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>3.485284403713478</v>
       </c>
       <c r="E59">
-        <v>-22.58340685500551</v>
+        <v>-15.17619097760713</v>
       </c>
       <c r="F59">
-        <v>-1.170183525182467</v>
+        <v>-1.84423172652927</v>
       </c>
       <c r="G59">
-        <v>-0.9132681064049192</v>
+        <v>-0.2329741719034652</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.30932627092809</v>
       </c>
       <c r="E60">
-        <v>-22.3588126581211</v>
+        <v>-16.70732238128857</v>
       </c>
       <c r="F60">
-        <v>-1.256847080287145</v>
+        <v>-1.297010654155647</v>
       </c>
       <c r="G60">
-        <v>-1.84322352220497</v>
+        <v>-0.9449069901237339</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.139555894273463</v>
       </c>
       <c r="E61">
-        <v>-21.10336569507861</v>
+        <v>-15.69121885497348</v>
       </c>
       <c r="F61">
-        <v>-1.152643190316018</v>
+        <v>-1.565350617055876</v>
       </c>
       <c r="G61">
-        <v>-0.5909103556094659</v>
+        <v>0.4384210161884279</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>2.979832009380627</v>
       </c>
       <c r="E62">
-        <v>-22.35866321847884</v>
+        <v>-14.52382354053614</v>
       </c>
       <c r="F62">
-        <v>-1.265648525912199</v>
+        <v>-1.264332466296469</v>
       </c>
       <c r="G62">
-        <v>-1.522385311812043</v>
+        <v>0.01562793482256536</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>2.839715379044356</v>
       </c>
       <c r="E63">
-        <v>-21.03700543697021</v>
+        <v>-13.95284183833101</v>
       </c>
       <c r="F63">
-        <v>-1.237090348992038</v>
+        <v>-1.857579199984594</v>
       </c>
       <c r="G63">
-        <v>-2.126563183274574</v>
+        <v>-0.8190334276295649</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.723118534739665</v>
       </c>
       <c r="E64">
-        <v>-20.20283335391328</v>
+        <v>-15.76919012043755</v>
       </c>
       <c r="F64">
-        <v>-1.22175453275988</v>
+        <v>-2.013318464150036</v>
       </c>
       <c r="G64">
-        <v>-3.025369676095623</v>
+        <v>-0.5537196870212934</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.630435918497259</v>
       </c>
       <c r="E65">
-        <v>-19.83976747882232</v>
+        <v>-16.31166055029039</v>
       </c>
       <c r="F65">
-        <v>-1.148123293633353</v>
+        <v>-1.647217918795645</v>
       </c>
       <c r="G65">
-        <v>-2.862639810112747</v>
+        <v>-1.301429570884466</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>2.570078008893211</v>
       </c>
       <c r="E66">
-        <v>-21.14682093165622</v>
+        <v>-14.01975457026835</v>
       </c>
       <c r="F66">
-        <v>-1.175302854554125</v>
+        <v>-1.427736075239681</v>
       </c>
       <c r="G66">
-        <v>-3.440161168893066</v>
+        <v>-0.8392807241477475</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>2.545203348911329</v>
       </c>
       <c r="E67">
-        <v>-21.09151920707454</v>
+        <v>-14.51757424640556</v>
       </c>
       <c r="F67">
-        <v>-1.070985729610044</v>
+        <v>-1.90974251357438</v>
       </c>
       <c r="G67">
-        <v>-2.220890557325028</v>
+        <v>-1.447474287349414</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>2.552853205168411</v>
       </c>
       <c r="E68">
-        <v>-20.08485754906545</v>
+        <v>-13.8857117396413</v>
       </c>
       <c r="F68">
-        <v>-1.428139920248118</v>
+        <v>-1.51055835164646</v>
       </c>
       <c r="G68">
-        <v>-3.055538677595001</v>
+        <v>-0.9913804284040229</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>2.598022651105119</v>
       </c>
       <c r="E69">
-        <v>-19.71402081257733</v>
+        <v>-14.06719939244671</v>
       </c>
       <c r="F69">
-        <v>-1.129475948332012</v>
+        <v>-1.337646964239908</v>
       </c>
       <c r="G69">
-        <v>-3.513645348228269</v>
+        <v>-1.893173033301494</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>2.682350519073454</v>
       </c>
       <c r="E70">
-        <v>-19.56515628652318</v>
+        <v>-13.33299790158311</v>
       </c>
       <c r="F70">
-        <v>-1.302876700866435</v>
+        <v>-1.563578450136499</v>
       </c>
       <c r="G70">
-        <v>-3.526609444560055</v>
+        <v>-2.383438343303243</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>2.800492857400011</v>
       </c>
       <c r="E71">
-        <v>-21.12609410612311</v>
+        <v>-14.49437940253827</v>
       </c>
       <c r="F71">
-        <v>-1.949221926487413</v>
+        <v>-1.388121255470878</v>
       </c>
       <c r="G71">
-        <v>-4.160218065866707</v>
+        <v>-2.185782221881057</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>2.951279673851162</v>
       </c>
       <c r="E72">
-        <v>-20.66525394873253</v>
+        <v>-13.03847048059824</v>
       </c>
       <c r="F72">
-        <v>-1.184308598242272</v>
+        <v>-2.131403536469989</v>
       </c>
       <c r="G72">
-        <v>-3.417745465046661</v>
+        <v>-2.755556904099481</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>3.134046269425009</v>
       </c>
       <c r="E73">
-        <v>-19.25274139320801</v>
+        <v>-13.1669704590399</v>
       </c>
       <c r="F73">
-        <v>-0.9885760085942372</v>
+        <v>-1.662987670448633</v>
       </c>
       <c r="G73">
-        <v>-3.384524140560075</v>
+        <v>-2.274564432153231</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>3.341708863849566</v>
       </c>
       <c r="E74">
-        <v>-18.6654798269453</v>
+        <v>-13.93686538203195</v>
       </c>
       <c r="F74">
-        <v>-0.983284847130754</v>
+        <v>-1.601875626583656</v>
       </c>
       <c r="G74">
-        <v>-4.11904812154033</v>
+        <v>-1.029335833011767</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>3.566884845893947</v>
       </c>
       <c r="E75">
-        <v>-21.46596060887278</v>
+        <v>-14.6045073619308</v>
       </c>
       <c r="F75">
-        <v>-1.58974443927139</v>
+        <v>-2.495126147392348</v>
       </c>
       <c r="G75">
-        <v>-3.318256950500484</v>
+        <v>-1.936170398765548</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>3.808349743723068</v>
       </c>
       <c r="E76">
-        <v>-20.00908259349511</v>
+        <v>-14.86550143288888</v>
       </c>
       <c r="F76">
-        <v>-1.493413151405912</v>
+        <v>-1.865524652562353</v>
       </c>
       <c r="G76">
-        <v>-3.865205421225633</v>
+        <v>-0.8832381478181902</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.059096867073</v>
       </c>
       <c r="E77">
-        <v>-20.92163350467679</v>
+        <v>-16.43477617313692</v>
       </c>
       <c r="F77">
-        <v>-1.197229262953384</v>
+        <v>-2.001127096012983</v>
       </c>
       <c r="G77">
-        <v>-4.827729984041035</v>
+        <v>-1.579690855096827</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>4.308533132736525</v>
       </c>
       <c r="E78">
-        <v>-20.82188027923583</v>
+        <v>-13.73577849372135</v>
       </c>
       <c r="F78">
-        <v>-1.543932578255473</v>
+        <v>-1.631435497495333</v>
       </c>
       <c r="G78">
-        <v>-3.56351871677739</v>
+        <v>-1.902478976812386</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>4.555621868168823</v>
       </c>
       <c r="E79">
-        <v>-20.78241462825898</v>
+        <v>-16.05412623347418</v>
       </c>
       <c r="F79">
-        <v>-1.349523174899788</v>
+        <v>-1.891933740555264</v>
       </c>
       <c r="G79">
-        <v>-4.853264221785434</v>
+        <v>-1.728546224724617</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>4.795844956381051</v>
       </c>
       <c r="E80">
-        <v>-21.62950644765979</v>
+        <v>-15.34052929934548</v>
       </c>
       <c r="F80">
-        <v>-1.349879508730762</v>
+        <v>-2.009619718984527</v>
       </c>
       <c r="G80">
-        <v>-5.183501070964352</v>
+        <v>-3.123411482241139</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>5.01856122455699</v>
       </c>
       <c r="E81">
-        <v>-23.02458890672879</v>
+        <v>-16.97229245242537</v>
       </c>
       <c r="F81">
-        <v>-1.498302843419831</v>
+        <v>-1.971612360719896</v>
       </c>
       <c r="G81">
-        <v>-4.48266851193726</v>
+        <v>-2.050728516606489</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.224081967487753</v>
       </c>
       <c r="E82">
-        <v>-22.33421398731143</v>
+        <v>-18.1004757104303</v>
       </c>
       <c r="F82">
-        <v>-2.09360047626845</v>
+        <v>-2.404152536638802</v>
       </c>
       <c r="G82">
-        <v>-3.424922727775801</v>
+        <v>-1.974599211385408</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>5.410664859655915</v>
       </c>
       <c r="E83">
-        <v>-21.95229154645252</v>
+        <v>-18.68551379595524</v>
       </c>
       <c r="F83">
-        <v>-1.848622551179826</v>
+        <v>-2.147291274213678</v>
       </c>
       <c r="G83">
-        <v>-4.84083643383101</v>
+        <v>-2.37409267324588</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>5.571130902123486</v>
       </c>
       <c r="E84">
-        <v>-24.54685808677722</v>
+        <v>-18.72155592058229</v>
       </c>
       <c r="F84">
-        <v>-1.670654390785276</v>
+        <v>-2.58777135973964</v>
       </c>
       <c r="G84">
-        <v>-3.375181781048252</v>
+        <v>-2.391569043147693</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.703980650601123</v>
       </c>
       <c r="E85">
-        <v>-25.23537180337743</v>
+        <v>-19.97599303392106</v>
       </c>
       <c r="F85">
-        <v>-1.627676571505038</v>
+        <v>-2.415129202338713</v>
       </c>
       <c r="G85">
-        <v>-4.941609440046424</v>
+        <v>-1.518647705898206</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.809944839758566</v>
       </c>
       <c r="E86">
-        <v>-24.06622396949912</v>
+        <v>-20.77977452791251</v>
       </c>
       <c r="F86">
-        <v>-2.060991179616594</v>
+        <v>-2.200054812345416</v>
       </c>
       <c r="G86">
-        <v>-4.332806736465532</v>
+        <v>-1.957761776772675</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.884221254338283</v>
       </c>
       <c r="E87">
-        <v>-26.74921802177159</v>
+        <v>-21.52180575033537</v>
       </c>
       <c r="F87">
-        <v>-2.145861979624994</v>
+        <v>-1.796208220202442</v>
       </c>
       <c r="G87">
-        <v>-5.131263972900192</v>
+        <v>-1.687730508770942</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.92065374170134</v>
       </c>
       <c r="E88">
-        <v>-27.40146771851838</v>
+        <v>-23.84047954021675</v>
       </c>
       <c r="F88">
-        <v>-1.60834031413048</v>
+        <v>-2.207219497906864</v>
       </c>
       <c r="G88">
-        <v>-5.088511587806044</v>
+        <v>-2.072680744077396</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.919273558510524</v>
       </c>
       <c r="E89">
-        <v>-29.25320149652085</v>
+        <v>-25.59302162355522</v>
       </c>
       <c r="F89">
-        <v>-1.966682284205133</v>
+        <v>-2.196131180939915</v>
       </c>
       <c r="G89">
-        <v>-4.343089290910508</v>
+        <v>-3.042352774712084</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.873106137629602</v>
       </c>
       <c r="E90">
-        <v>-30.32626869737842</v>
+        <v>-27.40094241553349</v>
       </c>
       <c r="F90">
-        <v>-1.565888285214168</v>
+        <v>-3.031937520783788</v>
       </c>
       <c r="G90">
-        <v>-3.864103009561056</v>
+        <v>-1.656144593780756</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.771821750023952</v>
       </c>
       <c r="E91">
-        <v>-32.72662936564717</v>
+        <v>-27.52171228884405</v>
       </c>
       <c r="F91">
-        <v>-1.352896468499674</v>
+        <v>-2.360786709409281</v>
       </c>
       <c r="G91">
-        <v>-5.368328828421863</v>
+        <v>-2.088084712471625</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.612722329575938</v>
       </c>
       <c r="E92">
-        <v>-34.26449913865202</v>
+        <v>-29.90324129795189</v>
       </c>
       <c r="F92">
-        <v>-1.372218472520993</v>
+        <v>-2.360486597138306</v>
       </c>
       <c r="G92">
-        <v>-5.366855635656886</v>
+        <v>-2.187344799375593</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.389324393437413</v>
       </c>
       <c r="E93">
-        <v>-34.69063533548481</v>
+        <v>-32.92697811269452</v>
       </c>
       <c r="F93">
-        <v>-1.580829758673381</v>
+        <v>-1.875722134951868</v>
       </c>
       <c r="G93">
-        <v>-5.217136213643347</v>
+        <v>-2.540017215674152</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.093146219359739</v>
       </c>
       <c r="E94">
-        <v>-37.74660582821404</v>
+        <v>-32.48334162805909</v>
       </c>
       <c r="F94">
-        <v>-1.493057609427896</v>
+        <v>-2.064827707196746</v>
       </c>
       <c r="G94">
-        <v>-4.305114023029528</v>
+        <v>-2.809740602940733</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.724661436859136</v>
       </c>
       <c r="E95">
-        <v>-39.76450969569098</v>
+        <v>-35.62175525433495</v>
       </c>
       <c r="F95">
-        <v>-1.401874949493512</v>
+        <v>-2.886215988386458</v>
       </c>
       <c r="G95">
-        <v>-5.220003146080356</v>
+        <v>-2.7129534935546</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.278244248061697</v>
       </c>
       <c r="E96">
-        <v>-40.99873396529651</v>
+        <v>-38.09483415821887</v>
       </c>
       <c r="F96">
-        <v>-0.9473774829099955</v>
+        <v>-2.460129414072967</v>
       </c>
       <c r="G96">
-        <v>-5.166551077803284</v>
+        <v>-4.043971569800738</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.761635377439204</v>
       </c>
       <c r="E97">
-        <v>-43.90646259714764</v>
+        <v>-41.22881214420422</v>
       </c>
       <c r="F97">
-        <v>-1.421984055354804</v>
+        <v>-1.831485269468855</v>
       </c>
       <c r="G97">
-        <v>-5.751014650579455</v>
+        <v>-2.679056817778003</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.161452795329482</v>
       </c>
       <c r="E98">
-        <v>-46.04257775012081</v>
+        <v>-42.43591311874081</v>
       </c>
       <c r="F98">
-        <v>-1.197488198870559</v>
+        <v>-2.527433748067313</v>
       </c>
       <c r="G98">
-        <v>-6.324993725632754</v>
+        <v>-2.931750758790573</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.51162045141898</v>
       </c>
       <c r="E99">
-        <v>-47.72602664128724</v>
+        <v>-44.14135907239951</v>
       </c>
       <c r="F99">
-        <v>-0.878428470322466</v>
+        <v>-2.80980376167242</v>
       </c>
       <c r="G99">
-        <v>-5.605185119574559</v>
+        <v>-4.399822109816999</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.779961374515838</v>
       </c>
       <c r="E100">
-        <v>-50.76834378488333</v>
+        <v>-47.21888057293123</v>
       </c>
       <c r="F100">
-        <v>-1.050602642625381</v>
+        <v>-2.546219667636255</v>
       </c>
       <c r="G100">
-        <v>-5.485280470687695</v>
+        <v>-3.356957227854564</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.037693943614266</v>
       </c>
       <c r="E101">
-        <v>-52.47091755390267</v>
+        <v>-49.50616298099145</v>
       </c>
       <c r="F101">
-        <v>-1.804165550574567</v>
+        <v>-2.607615986713054</v>
       </c>
       <c r="G101">
-        <v>-7.052909857716624</v>
+        <v>-4.647570095793896</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.1964538530899932</v>
       </c>
       <c r="E102">
-        <v>-55.14248400201678</v>
+        <v>-51.93452999676063</v>
       </c>
       <c r="F102">
-        <v>-0.9520541664782881</v>
+        <v>-1.888464632747494</v>
       </c>
       <c r="G102">
-        <v>-5.809098172065967</v>
+        <v>-4.706431595482139</v>
       </c>
     </row>
   </sheetData>
